--- a/data/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ114"/>
+  <dimension ref="A1:AJ127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -14490,8 +14490,1438 @@
       <c r="AI114" s="2" t="inlineStr"/>
       <c r="AJ114" s="2" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2ccf46ab0ab040ed</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>888-2026:179014</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>0.821797</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>0.590164</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr"/>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>0.231633</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:52.794231Z</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:00Z</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr"/>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=2ccf46ab0ab040ed;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
+      <c r="AB115" s="2" t="inlineStr"/>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr"/>
+      <c r="AE115" s="2" t="inlineStr"/>
+      <c r="AF115" s="2" t="inlineStr"/>
+      <c r="AG115" s="2" t="inlineStr"/>
+      <c r="AH115" s="2" t="inlineStr"/>
+      <c r="AI115" s="2" t="inlineStr"/>
+      <c r="AJ115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>a7f951016379499b</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>1067-2026:179469</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>0.639939</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>0.490196</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>0.149743</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:42.019193Z</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr"/>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=a7f951016379499b;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
+      <c r="AB116" s="2" t="inlineStr"/>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr"/>
+      <c r="AE116" s="2" t="inlineStr"/>
+      <c r="AF116" s="2" t="inlineStr"/>
+      <c r="AG116" s="2" t="inlineStr"/>
+      <c r="AH116" s="2" t="inlineStr"/>
+      <c r="AI116" s="2" t="inlineStr"/>
+      <c r="AJ116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>c0cf59bfb705465c</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182259</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>0.530496</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>0.509804</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr"/>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>0.020692</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:40.733235Z</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:30Z</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr"/>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=c0cf59bfb705465c;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
+      <c r="AB117" s="2" t="inlineStr"/>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr"/>
+      <c r="AE117" s="2" t="inlineStr"/>
+      <c r="AF117" s="2" t="inlineStr"/>
+      <c r="AG117" s="2" t="inlineStr"/>
+      <c r="AH117" s="2" t="inlineStr"/>
+      <c r="AI117" s="2" t="inlineStr"/>
+      <c r="AJ117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>1631795568fd45da</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182280</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>0.597848</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>0.590164</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr"/>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>0.007684</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:41.086960Z</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:30Z</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr"/>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=1631795568fd45da;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr"/>
+      <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
+      <c r="AB118" s="2" t="inlineStr"/>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr"/>
+      <c r="AE118" s="2" t="inlineStr"/>
+      <c r="AF118" s="2" t="inlineStr"/>
+      <c r="AG118" s="2" t="inlineStr"/>
+      <c r="AH118" s="2" t="inlineStr"/>
+      <c r="AI118" s="2" t="inlineStr"/>
+      <c r="AJ118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>aa80b38afdc44bf2</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182257</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>0.549832</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>0.509804</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr"/>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>0.040028</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:48.248249Z</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr"/>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=aa80b38afdc44bf2;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr"/>
+      <c r="AE119" s="2" t="inlineStr"/>
+      <c r="AF119" s="2" t="inlineStr"/>
+      <c r="AG119" s="2" t="inlineStr"/>
+      <c r="AH119" s="2" t="inlineStr"/>
+      <c r="AI119" s="2" t="inlineStr"/>
+      <c r="AJ119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>d1fcb39b0d8f4e1a</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182268</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>0.529270</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>0.600000</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr"/>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>-0.070730</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:44.674546Z</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr"/>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=d1fcb39b0d8f4e1a;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
+      <c r="AB120" s="2" t="inlineStr"/>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr"/>
+      <c r="AE120" s="2" t="inlineStr"/>
+      <c r="AF120" s="2" t="inlineStr"/>
+      <c r="AG120" s="2" t="inlineStr"/>
+      <c r="AH120" s="2" t="inlineStr"/>
+      <c r="AI120" s="2" t="inlineStr"/>
+      <c r="AJ120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>c061c5b94c184f35</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182284</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>0.736958</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>0.699700</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr"/>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>0.037258</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:43.798568Z</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr"/>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=c061c5b94c184f35;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
+      <c r="AB121" s="2" t="inlineStr"/>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr"/>
+      <c r="AE121" s="2" t="inlineStr"/>
+      <c r="AF121" s="2" t="inlineStr"/>
+      <c r="AG121" s="2" t="inlineStr"/>
+      <c r="AH121" s="2" t="inlineStr"/>
+      <c r="AI121" s="2" t="inlineStr"/>
+      <c r="AJ121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>68186bba3f2b4e2e</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182241</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>0.530510</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>0.460829</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr"/>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>0.069681</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:49.636292Z</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:30Z</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr"/>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=68186bba3f2b4e2e;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr"/>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr"/>
+      <c r="AE122" s="2" t="inlineStr"/>
+      <c r="AF122" s="2" t="inlineStr"/>
+      <c r="AG122" s="2" t="inlineStr"/>
+      <c r="AH122" s="2" t="inlineStr"/>
+      <c r="AI122" s="2" t="inlineStr"/>
+      <c r="AJ122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>e5a2586d0b754134</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>0.756798</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>0.650350</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>0.106448</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:51.741348Z</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr"/>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=e5a2586d0b754134;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr"/>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr"/>
+      <c r="AE123" s="2" t="inlineStr"/>
+      <c r="AF123" s="2" t="inlineStr"/>
+      <c r="AG123" s="2" t="inlineStr"/>
+      <c r="AH123" s="2" t="inlineStr"/>
+      <c r="AI123" s="2" t="inlineStr"/>
+      <c r="AJ123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>8c5a4b8f1d9449a4</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182240</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>0.763762</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>0.859944</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>-0.096182</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:54.553392Z</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00Z</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=8c5a4b8f1d9449a4;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
+      <c r="AB124" s="2" t="inlineStr"/>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr"/>
+      <c r="AE124" s="2" t="inlineStr"/>
+      <c r="AF124" s="2" t="inlineStr"/>
+      <c r="AG124" s="2" t="inlineStr"/>
+      <c r="AH124" s="2" t="inlineStr"/>
+      <c r="AI124" s="2" t="inlineStr"/>
+      <c r="AJ124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>6240c2227d994ec7</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182283</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>0.578226</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>0.590164</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr"/>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>-0.011938</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:55.125883Z</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=6240c2227d994ec7;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr"/>
+      <c r="AB125" s="2" t="inlineStr"/>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr"/>
+      <c r="AE125" s="2" t="inlineStr"/>
+      <c r="AF125" s="2" t="inlineStr"/>
+      <c r="AG125" s="2" t="inlineStr"/>
+      <c r="AH125" s="2" t="inlineStr"/>
+      <c r="AI125" s="2" t="inlineStr"/>
+      <c r="AJ125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>d8eff19de3f843cc</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182274</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>0.617346</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>0.600000</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0.017346</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:55.388422Z</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=d8eff19de3f843cc;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
+      <c r="AB126" s="2" t="inlineStr"/>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr"/>
+      <c r="AE126" s="2" t="inlineStr"/>
+      <c r="AF126" s="2" t="inlineStr"/>
+      <c r="AG126" s="2" t="inlineStr"/>
+      <c r="AH126" s="2" t="inlineStr"/>
+      <c r="AI126" s="2" t="inlineStr"/>
+      <c r="AJ126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>fc4cd1d6df72434b</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>999faa03e2fa83bdf40e3760cb8645b4c314e4cc37c2050b8320d6582c4d8167</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182281</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>0.630736</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>0.050000</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>0.650350</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>-0.019614</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:46:55.697720Z</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/tennis.xlsx;original_pick_id=fc4cd1d6df72434b;original_record_type=RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr"/>
+      <c r="AB127" s="2" t="inlineStr"/>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr"/>
+      <c r="AE127" s="2" t="inlineStr"/>
+      <c r="AF127" s="2" t="inlineStr"/>
+      <c r="AG127" s="2" t="inlineStr"/>
+      <c r="AH127" s="2" t="inlineStr"/>
+      <c r="AI127" s="2" t="inlineStr"/>
+      <c r="AJ127" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ114"/>
+  <autoFilter ref="A1:AJ127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ127"/>
+  <dimension ref="A1:AJ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -15920,8 +15920,1598 @@
       <c r="AI127" s="2" t="inlineStr"/>
       <c r="AJ127" s="2" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>11bbf0ab86fa477f</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>1067-2026:179469</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>0.639939</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0.1497429215686275</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:46.960029Z</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:30Z</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+      <c r="AB128" s="2" t="inlineStr"/>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr"/>
+      <c r="AE128" s="2" t="inlineStr"/>
+      <c r="AF128" s="2" t="inlineStr"/>
+      <c r="AG128" s="2" t="inlineStr"/>
+      <c r="AH128" s="2" t="inlineStr"/>
+      <c r="AI128" s="2" t="inlineStr"/>
+      <c r="AJ128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>ba987c71a1504d32</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182257</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>0.549832</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0.04002807843137257</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:51.852853Z</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+      <c r="AB129" s="2" t="inlineStr"/>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr"/>
+      <c r="AE129" s="2" t="inlineStr"/>
+      <c r="AF129" s="2" t="inlineStr"/>
+      <c r="AG129" s="2" t="inlineStr"/>
+      <c r="AH129" s="2" t="inlineStr"/>
+      <c r="AI129" s="2" t="inlineStr"/>
+      <c r="AJ129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>bda342f9f11349eb</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182268</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>0.52927</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>-0.07073000000000007</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:48.148287Z</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr"/>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+      <c r="AB130" s="2" t="inlineStr"/>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr"/>
+      <c r="AE130" s="2" t="inlineStr"/>
+      <c r="AF130" s="2" t="inlineStr"/>
+      <c r="AG130" s="2" t="inlineStr"/>
+      <c r="AH130" s="2" t="inlineStr"/>
+      <c r="AI130" s="2" t="inlineStr"/>
+      <c r="AJ130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>d19352c6115840a6</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>0.756798</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>0.6503496503496503</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr"/>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>0.10644834965034966</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:57.265599Z</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr"/>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+      <c r="AB131" s="2" t="inlineStr"/>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr"/>
+      <c r="AE131" s="2" t="inlineStr"/>
+      <c r="AF131" s="2" t="inlineStr"/>
+      <c r="AG131" s="2" t="inlineStr"/>
+      <c r="AH131" s="2" t="inlineStr"/>
+      <c r="AI131" s="2" t="inlineStr"/>
+      <c r="AJ131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>9f60afb9f6ee4f41</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182240</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>0.763762</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>0.8599439775910364</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>-0.0961819775910363</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:47:57.823493Z</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00Z</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr"/>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr"/>
+      <c r="AB132" s="2" t="inlineStr"/>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr"/>
+      <c r="AE132" s="2" t="inlineStr"/>
+      <c r="AF132" s="2" t="inlineStr"/>
+      <c r="AG132" s="2" t="inlineStr"/>
+      <c r="AH132" s="2" t="inlineStr"/>
+      <c r="AI132" s="2" t="inlineStr"/>
+      <c r="AJ132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>e8ac81fb273c4d5d</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182283</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>0.578226</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>-0.01193793442622948</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:00.384778Z</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr"/>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr"/>
+      <c r="AB133" s="2" t="inlineStr"/>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr"/>
+      <c r="AE133" s="2" t="inlineStr"/>
+      <c r="AF133" s="2" t="inlineStr"/>
+      <c r="AG133" s="2" t="inlineStr"/>
+      <c r="AH133" s="2" t="inlineStr"/>
+      <c r="AI133" s="2" t="inlineStr"/>
+      <c r="AJ133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2bfecafe57a946a7</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182274</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>0.617346</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>0.01734599999999986</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:00.569912Z</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr"/>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr"/>
+      <c r="AB134" s="2" t="inlineStr"/>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="inlineStr"/>
+      <c r="AE134" s="2" t="inlineStr"/>
+      <c r="AF134" s="2" t="inlineStr"/>
+      <c r="AG134" s="2" t="inlineStr"/>
+      <c r="AH134" s="2" t="inlineStr"/>
+      <c r="AI134" s="2" t="inlineStr"/>
+      <c r="AJ134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>387511b991374747</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182281</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>0.630736</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>-0.029127945578231396</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:00.878431Z</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr"/>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
+      <c r="AB135" s="2" t="inlineStr"/>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr"/>
+      <c r="AE135" s="2" t="inlineStr"/>
+      <c r="AF135" s="2" t="inlineStr"/>
+      <c r="AG135" s="2" t="inlineStr"/>
+      <c r="AH135" s="2" t="inlineStr"/>
+      <c r="AI135" s="2" t="inlineStr"/>
+      <c r="AJ135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>a50a47d717bc4247</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>888-2026:178979</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>0.592585</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>0.002421065573770531</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:13.867147Z</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:30Z</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr"/>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr"/>
+      <c r="AB136" s="2" t="inlineStr"/>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr"/>
+      <c r="AE136" s="2" t="inlineStr"/>
+      <c r="AF136" s="2" t="inlineStr"/>
+      <c r="AG136" s="2" t="inlineStr"/>
+      <c r="AH136" s="2" t="inlineStr"/>
+      <c r="AI136" s="2" t="inlineStr"/>
+      <c r="AJ136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>c20043fdd7ca4c5e</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181785</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>0.561017</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0.07082092156862746</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:12.259620Z</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr"/>
+      <c r="AB137" s="2" t="inlineStr"/>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr"/>
+      <c r="AE137" s="2" t="inlineStr"/>
+      <c r="AF137" s="2" t="inlineStr"/>
+      <c r="AG137" s="2" t="inlineStr"/>
+      <c r="AH137" s="2" t="inlineStr"/>
+      <c r="AI137" s="2" t="inlineStr"/>
+      <c r="AJ137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>1ae585d192104ef0</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181836</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>0.567487</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>0.07729092156862744</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:10.755068Z</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00Z</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
+      <c r="AB138" s="2" t="inlineStr"/>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr"/>
+      <c r="AE138" s="2" t="inlineStr"/>
+      <c r="AF138" s="2" t="inlineStr"/>
+      <c r="AG138" s="2" t="inlineStr"/>
+      <c r="AH138" s="2" t="inlineStr"/>
+      <c r="AI138" s="2" t="inlineStr"/>
+      <c r="AJ138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>6766256c39a94af6</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181781</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>0.529427</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>-0.04138845064377683</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:16.186106Z</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:00Z</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
+      <c r="AB139" s="2" t="inlineStr"/>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr"/>
+      <c r="AE139" s="2" t="inlineStr"/>
+      <c r="AF139" s="2" t="inlineStr"/>
+      <c r="AG139" s="2" t="inlineStr"/>
+      <c r="AH139" s="2" t="inlineStr"/>
+      <c r="AI139" s="2" t="inlineStr"/>
+      <c r="AJ139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>6d35e76671d0436c</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181801</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>0.584559</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>0.04538849308755766</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:17.140267Z</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
+      <c r="AB140" s="2" t="inlineStr"/>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr"/>
+      <c r="AE140" s="2" t="inlineStr"/>
+      <c r="AF140" s="2" t="inlineStr"/>
+      <c r="AG140" s="2" t="inlineStr"/>
+      <c r="AH140" s="2" t="inlineStr"/>
+      <c r="AI140" s="2" t="inlineStr"/>
+      <c r="AJ140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>4db08b05bdb84580</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181798</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>0.552246</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>0.02172956807511739</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:19.678581Z</t>
+        </is>
+      </c>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:30Z</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr"/>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr"/>
+      <c r="AB141" s="2" t="inlineStr"/>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr"/>
+      <c r="AE141" s="2" t="inlineStr"/>
+      <c r="AF141" s="2" t="inlineStr"/>
+      <c r="AG141" s="2" t="inlineStr"/>
+      <c r="AH141" s="2" t="inlineStr"/>
+      <c r="AI141" s="2" t="inlineStr"/>
+      <c r="AJ141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>79b552958eef44b6</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>0.57909</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>0.08889392156862747</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:48:20.160476Z</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr"/>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
+      <c r="AB142" s="2" t="inlineStr"/>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr"/>
+      <c r="AE142" s="2" t="inlineStr"/>
+      <c r="AF142" s="2" t="inlineStr"/>
+      <c r="AG142" s="2" t="inlineStr"/>
+      <c r="AH142" s="2" t="inlineStr"/>
+      <c r="AI142" s="2" t="inlineStr"/>
+      <c r="AJ142" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ127"/>
+  <autoFilter ref="A1:AJ142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ142"/>
+  <dimension ref="A1:AJ153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -17510,8 +17510,1174 @@
       <c r="AI142" s="2" t="inlineStr"/>
       <c r="AJ142" s="2" t="inlineStr"/>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>7731f95f6722460e</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182240</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>0.763762</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>0.8599439775910364</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr"/>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>-0.0961819775910363</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:42.770965Z</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00Z</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr"/>
+      <c r="W143" s="2" t="inlineStr"/>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr"/>
+      <c r="AB143" s="2" t="inlineStr"/>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr"/>
+      <c r="AE143" s="2" t="inlineStr"/>
+      <c r="AF143" s="2" t="inlineStr"/>
+      <c r="AG143" s="2" t="inlineStr"/>
+      <c r="AH143" s="2" t="inlineStr"/>
+      <c r="AI143" s="2" t="inlineStr"/>
+      <c r="AJ143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>1e5c47f821814c6e</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182274</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>0.617346</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>0.01734599999999986</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:45.629044Z</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+      <c r="AB144" s="2" t="inlineStr"/>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr"/>
+      <c r="AE144" s="2" t="inlineStr"/>
+      <c r="AF144" s="2" t="inlineStr"/>
+      <c r="AG144" s="2" t="inlineStr"/>
+      <c r="AH144" s="2" t="inlineStr"/>
+      <c r="AI144" s="2" t="inlineStr"/>
+      <c r="AJ144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>a2d4b6768b58410b</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182281</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>0.630736</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>-0.029127945578231396</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:45:45.782209Z</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
+      <c r="AB145" s="2" t="inlineStr"/>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr"/>
+      <c r="AE145" s="2" t="inlineStr"/>
+      <c r="AF145" s="2" t="inlineStr"/>
+      <c r="AG145" s="2" t="inlineStr"/>
+      <c r="AH145" s="2" t="inlineStr"/>
+      <c r="AI145" s="2" t="inlineStr"/>
+      <c r="AJ145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>90a737889ee24b4f</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181781</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>0.529427</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>-0.04138845064377683</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:43:28.084029Z</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:00Z</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr"/>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
+      <c r="AB146" s="2" t="inlineStr"/>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr"/>
+      <c r="AE146" s="2" t="inlineStr"/>
+      <c r="AF146" s="2" t="inlineStr"/>
+      <c r="AG146" s="2" t="inlineStr"/>
+      <c r="AH146" s="2" t="inlineStr"/>
+      <c r="AI146" s="2" t="inlineStr"/>
+      <c r="AJ146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>c04522c9a8734317</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181801</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>0.584559</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr"/>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>0.04538849308755766</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:43:29.378530Z</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr"/>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr"/>
+      <c r="AB147" s="2" t="inlineStr"/>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr"/>
+      <c r="AE147" s="2" t="inlineStr"/>
+      <c r="AF147" s="2" t="inlineStr"/>
+      <c r="AG147" s="2" t="inlineStr"/>
+      <c r="AH147" s="2" t="inlineStr"/>
+      <c r="AI147" s="2" t="inlineStr"/>
+      <c r="AJ147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>b83e95c08a7943d1</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181798</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>0.552246</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>0.013075493087557621</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:43:31.804327Z</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:30Z</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr"/>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
+      <c r="AB148" s="2" t="inlineStr"/>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr"/>
+      <c r="AE148" s="2" t="inlineStr"/>
+      <c r="AF148" s="2" t="inlineStr"/>
+      <c r="AG148" s="2" t="inlineStr"/>
+      <c r="AH148" s="2" t="inlineStr"/>
+      <c r="AI148" s="2" t="inlineStr"/>
+      <c r="AJ148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>6040b395fde94685</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>0.57909</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>0.08889392156862747</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:43:32.205224Z</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr"/>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+      <c r="AB149" s="2" t="inlineStr"/>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr"/>
+      <c r="AE149" s="2" t="inlineStr"/>
+      <c r="AF149" s="2" t="inlineStr"/>
+      <c r="AG149" s="2" t="inlineStr"/>
+      <c r="AH149" s="2" t="inlineStr"/>
+      <c r="AI149" s="2" t="inlineStr"/>
+      <c r="AJ149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>e64176f1288e4351</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181781</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>0.529427</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>-0.04138845064377683</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:46:00.985324Z</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:00Z</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr"/>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr"/>
+      <c r="AB150" s="2" t="inlineStr"/>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr"/>
+      <c r="AE150" s="2" t="inlineStr"/>
+      <c r="AF150" s="2" t="inlineStr"/>
+      <c r="AG150" s="2" t="inlineStr"/>
+      <c r="AH150" s="2" t="inlineStr"/>
+      <c r="AI150" s="2" t="inlineStr"/>
+      <c r="AJ150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>dbeeb27c3b824ed4</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181801</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>0.584559</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>0.04538849308755766</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:46:02.075374Z</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr"/>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr"/>
+      <c r="AB151" s="2" t="inlineStr"/>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr"/>
+      <c r="AE151" s="2" t="inlineStr"/>
+      <c r="AF151" s="2" t="inlineStr"/>
+      <c r="AG151" s="2" t="inlineStr"/>
+      <c r="AH151" s="2" t="inlineStr"/>
+      <c r="AI151" s="2" t="inlineStr"/>
+      <c r="AJ151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>8d95e6e27daf4575</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181798</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>0.552246</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>0.013075493087557621</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:46:04.691160Z</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:30Z</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr"/>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
+      <c r="AB152" s="2" t="inlineStr"/>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr"/>
+      <c r="AE152" s="2" t="inlineStr"/>
+      <c r="AF152" s="2" t="inlineStr"/>
+      <c r="AG152" s="2" t="inlineStr"/>
+      <c r="AH152" s="2" t="inlineStr"/>
+      <c r="AI152" s="2" t="inlineStr"/>
+      <c r="AJ152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>fc9627153b0247b2</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>0.57909</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr"/>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>0.08889392156862747</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:46:04.980434Z</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr"/>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
+      <c r="AB153" s="2" t="inlineStr"/>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr"/>
+      <c r="AE153" s="2" t="inlineStr"/>
+      <c r="AF153" s="2" t="inlineStr"/>
+      <c r="AG153" s="2" t="inlineStr"/>
+      <c r="AH153" s="2" t="inlineStr"/>
+      <c r="AI153" s="2" t="inlineStr"/>
+      <c r="AJ153" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ142"/>
+  <autoFilter ref="A1:AJ153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ153"/>
+  <dimension ref="A1:AJ171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -18676,8 +18676,1916 @@
       <c r="AI153" s="2" t="inlineStr"/>
       <c r="AJ153" s="2" t="inlineStr"/>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>4cd8689d5f374c1f</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>0.756798</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>0.09693405442176861</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:21.762166Z</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr"/>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
+      <c r="AB154" s="2" t="inlineStr"/>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr"/>
+      <c r="AE154" s="2" t="inlineStr"/>
+      <c r="AF154" s="2" t="inlineStr"/>
+      <c r="AG154" s="2" t="inlineStr"/>
+      <c r="AH154" s="2" t="inlineStr"/>
+      <c r="AI154" s="2" t="inlineStr"/>
+      <c r="AJ154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>440bdfc3cb724400</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182240</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>0.763762</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>0.8599439775910364</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr"/>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>-0.0961819775910363</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:22.316753Z</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00Z</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr"/>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
+      <c r="AB155" s="2" t="inlineStr"/>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr"/>
+      <c r="AE155" s="2" t="inlineStr"/>
+      <c r="AF155" s="2" t="inlineStr"/>
+      <c r="AG155" s="2" t="inlineStr"/>
+      <c r="AH155" s="2" t="inlineStr"/>
+      <c r="AI155" s="2" t="inlineStr"/>
+      <c r="AJ155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>4f70f9667fb649a1</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182283</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>0.578226</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr"/>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>-0.01193793442622948</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:24.563955Z</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
+      <c r="AB156" s="2" t="inlineStr"/>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr"/>
+      <c r="AE156" s="2" t="inlineStr"/>
+      <c r="AF156" s="2" t="inlineStr"/>
+      <c r="AG156" s="2" t="inlineStr"/>
+      <c r="AH156" s="2" t="inlineStr"/>
+      <c r="AI156" s="2" t="inlineStr"/>
+      <c r="AJ156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>0daf2c84b8bc4597</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182274</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>0.617346</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>0.01734599999999986</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:24.936697Z</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+      <c r="AB157" s="2" t="inlineStr"/>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr"/>
+      <c r="AE157" s="2" t="inlineStr"/>
+      <c r="AF157" s="2" t="inlineStr"/>
+      <c r="AG157" s="2" t="inlineStr"/>
+      <c r="AH157" s="2" t="inlineStr"/>
+      <c r="AI157" s="2" t="inlineStr"/>
+      <c r="AJ157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>01fb58222fdc433e</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182281</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>0.630736</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>-0.029127945578231396</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:25.259675Z</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+      <c r="AB158" s="2" t="inlineStr"/>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr"/>
+      <c r="AE158" s="2" t="inlineStr"/>
+      <c r="AF158" s="2" t="inlineStr"/>
+      <c r="AG158" s="2" t="inlineStr"/>
+      <c r="AH158" s="2" t="inlineStr"/>
+      <c r="AI158" s="2" t="inlineStr"/>
+      <c r="AJ158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>eb8d81c1aa444603</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181781</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>0.529427</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>-0.04138845064377683</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:40.263421Z</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:00Z</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+      <c r="AB159" s="2" t="inlineStr"/>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr"/>
+      <c r="AE159" s="2" t="inlineStr"/>
+      <c r="AF159" s="2" t="inlineStr"/>
+      <c r="AG159" s="2" t="inlineStr"/>
+      <c r="AH159" s="2" t="inlineStr"/>
+      <c r="AI159" s="2" t="inlineStr"/>
+      <c r="AJ159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>12e516e7f8ed46a8</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181801</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>0.584559</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>0.04538849308755766</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:41.544451Z</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr"/>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
+      <c r="AB160" s="2" t="inlineStr"/>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr"/>
+      <c r="AE160" s="2" t="inlineStr"/>
+      <c r="AF160" s="2" t="inlineStr"/>
+      <c r="AG160" s="2" t="inlineStr"/>
+      <c r="AH160" s="2" t="inlineStr"/>
+      <c r="AI160" s="2" t="inlineStr"/>
+      <c r="AJ160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>86e7297fa598497b</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181798</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>0.552246</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>0.013075493087557621</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:43.874434Z</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:30Z</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr"/>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
+      <c r="AB161" s="2" t="inlineStr"/>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr"/>
+      <c r="AE161" s="2" t="inlineStr"/>
+      <c r="AF161" s="2" t="inlineStr"/>
+      <c r="AG161" s="2" t="inlineStr"/>
+      <c r="AH161" s="2" t="inlineStr"/>
+      <c r="AI161" s="2" t="inlineStr"/>
+      <c r="AJ161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>21584dabb9774970</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>0.57909</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>0.08889392156862747</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:04:44.346278Z</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+      <c r="AB162" s="2" t="inlineStr"/>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr"/>
+      <c r="AE162" s="2" t="inlineStr"/>
+      <c r="AF162" s="2" t="inlineStr"/>
+      <c r="AG162" s="2" t="inlineStr"/>
+      <c r="AH162" s="2" t="inlineStr"/>
+      <c r="AI162" s="2" t="inlineStr"/>
+      <c r="AJ162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>930d98b9a1754101</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>0.756798</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr"/>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>0.09693405442176861</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:16.585959Z</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
+      <c r="AB163" s="2" t="inlineStr"/>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr"/>
+      <c r="AE163" s="2" t="inlineStr"/>
+      <c r="AF163" s="2" t="inlineStr"/>
+      <c r="AG163" s="2" t="inlineStr"/>
+      <c r="AH163" s="2" t="inlineStr"/>
+      <c r="AI163" s="2" t="inlineStr"/>
+      <c r="AJ163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ce0d2e9cfbd14342</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182240</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>0.763762</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>0.8599439775910364</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>-0.0961819775910363</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:17.166108Z</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00Z</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+      <c r="AB164" s="2" t="inlineStr"/>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr"/>
+      <c r="AE164" s="2" t="inlineStr"/>
+      <c r="AF164" s="2" t="inlineStr"/>
+      <c r="AG164" s="2" t="inlineStr"/>
+      <c r="AH164" s="2" t="inlineStr"/>
+      <c r="AI164" s="2" t="inlineStr"/>
+      <c r="AJ164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>c34bdb60b61047b6</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182283</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>0.578226</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>-0.01193793442622948</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:19.531915Z</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+      <c r="AB165" s="2" t="inlineStr"/>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr"/>
+      <c r="AE165" s="2" t="inlineStr"/>
+      <c r="AF165" s="2" t="inlineStr"/>
+      <c r="AG165" s="2" t="inlineStr"/>
+      <c r="AH165" s="2" t="inlineStr"/>
+      <c r="AI165" s="2" t="inlineStr"/>
+      <c r="AJ165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>7a2937eb125d4ad3</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182274</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>0.617346</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0.01734599999999986</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:19.788447Z</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr"/>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+      <c r="AB166" s="2" t="inlineStr"/>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr"/>
+      <c r="AE166" s="2" t="inlineStr"/>
+      <c r="AF166" s="2" t="inlineStr"/>
+      <c r="AG166" s="2" t="inlineStr"/>
+      <c r="AH166" s="2" t="inlineStr"/>
+      <c r="AI166" s="2" t="inlineStr"/>
+      <c r="AJ166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>a05c02694d724101</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182281</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>0.630736</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>-0.029127945578231396</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:20.067983Z</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr"/>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+      <c r="AB167" s="2" t="inlineStr"/>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr"/>
+      <c r="AE167" s="2" t="inlineStr"/>
+      <c r="AF167" s="2" t="inlineStr"/>
+      <c r="AG167" s="2" t="inlineStr"/>
+      <c r="AH167" s="2" t="inlineStr"/>
+      <c r="AI167" s="2" t="inlineStr"/>
+      <c r="AJ167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>db4de0354af14057</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181781</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>0.529427</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>-0.04138845064377683</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:35.252381Z</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:00Z</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
+      <c r="AB168" s="2" t="inlineStr"/>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr"/>
+      <c r="AE168" s="2" t="inlineStr"/>
+      <c r="AF168" s="2" t="inlineStr"/>
+      <c r="AG168" s="2" t="inlineStr"/>
+      <c r="AH168" s="2" t="inlineStr"/>
+      <c r="AI168" s="2" t="inlineStr"/>
+      <c r="AJ168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>5eb80b0224f74dcf</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181801</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>0.584559</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>0.04538849308755766</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:36.379310Z</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr"/>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
+      <c r="AB169" s="2" t="inlineStr"/>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr"/>
+      <c r="AE169" s="2" t="inlineStr"/>
+      <c r="AF169" s="2" t="inlineStr"/>
+      <c r="AG169" s="2" t="inlineStr"/>
+      <c r="AH169" s="2" t="inlineStr"/>
+      <c r="AI169" s="2" t="inlineStr"/>
+      <c r="AJ169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>cc7e481a29664c83</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181798</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>0.552246</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr"/>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>0.013075493087557621</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:38.859418Z</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:30Z</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
+      <c r="AB170" s="2" t="inlineStr"/>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr"/>
+      <c r="AE170" s="2" t="inlineStr"/>
+      <c r="AF170" s="2" t="inlineStr"/>
+      <c r="AG170" s="2" t="inlineStr"/>
+      <c r="AH170" s="2" t="inlineStr"/>
+      <c r="AI170" s="2" t="inlineStr"/>
+      <c r="AJ170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>575fac36e69b45f8</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>0.57909</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>0.08889392156862747</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:08:39.325449Z</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr"/>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
+      <c r="AB171" s="2" t="inlineStr"/>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr"/>
+      <c r="AE171" s="2" t="inlineStr"/>
+      <c r="AF171" s="2" t="inlineStr"/>
+      <c r="AG171" s="2" t="inlineStr"/>
+      <c r="AH171" s="2" t="inlineStr"/>
+      <c r="AI171" s="2" t="inlineStr"/>
+      <c r="AJ171" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ153"/>
+  <autoFilter ref="A1:AJ171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ171"/>
+  <dimension ref="A1:AJ180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -20584,8 +20584,962 @@
       <c r="AI171" s="2" t="inlineStr"/>
       <c r="AJ171" s="2" t="inlineStr"/>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>bddec47a43cf4ff8</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182273</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>0.756798</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>0.09693405442176861</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:22.826331Z</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T20:00Z</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr"/>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
+      <c r="AB172" s="2" t="inlineStr"/>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr"/>
+      <c r="AE172" s="2" t="inlineStr"/>
+      <c r="AF172" s="2" t="inlineStr"/>
+      <c r="AG172" s="2" t="inlineStr"/>
+      <c r="AH172" s="2" t="inlineStr"/>
+      <c r="AI172" s="2" t="inlineStr"/>
+      <c r="AJ172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>5433376be51b470c</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182240</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>0.763762</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>0.8599439775910364</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr"/>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>-0.0961819775910363</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:23.926382Z</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00Z</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+      <c r="AB173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr"/>
+      <c r="AE173" s="2" t="inlineStr"/>
+      <c r="AF173" s="2" t="inlineStr"/>
+      <c r="AG173" s="2" t="inlineStr"/>
+      <c r="AH173" s="2" t="inlineStr"/>
+      <c r="AI173" s="2" t="inlineStr"/>
+      <c r="AJ173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>41d9df3c950e4a7c</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182283</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>0.578226</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr"/>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>-0.01193793442622948</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:26.302412Z</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:30Z</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+      <c r="AB174" s="2" t="inlineStr"/>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr"/>
+      <c r="AE174" s="2" t="inlineStr"/>
+      <c r="AF174" s="2" t="inlineStr"/>
+      <c r="AG174" s="2" t="inlineStr"/>
+      <c r="AH174" s="2" t="inlineStr"/>
+      <c r="AI174" s="2" t="inlineStr"/>
+      <c r="AJ174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>7e84056f19794799</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182274</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>0.617346</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr"/>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>0.01734599999999986</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:26.656599Z</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+      <c r="AB175" s="2" t="inlineStr"/>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr"/>
+      <c r="AE175" s="2" t="inlineStr"/>
+      <c r="AF175" s="2" t="inlineStr"/>
+      <c r="AG175" s="2" t="inlineStr"/>
+      <c r="AH175" s="2" t="inlineStr"/>
+      <c r="AI175" s="2" t="inlineStr"/>
+      <c r="AJ175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>a45672072b5b4779</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182281</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>0.630736</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr"/>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>-0.029127945578231396</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:26.839958Z</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+      <c r="AB176" s="2" t="inlineStr"/>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr"/>
+      <c r="AE176" s="2" t="inlineStr"/>
+      <c r="AF176" s="2" t="inlineStr"/>
+      <c r="AG176" s="2" t="inlineStr"/>
+      <c r="AH176" s="2" t="inlineStr"/>
+      <c r="AI176" s="2" t="inlineStr"/>
+      <c r="AJ176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>8edbc26a4bc64080</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181781</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>0.529427</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr"/>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>-0.04138845064377683</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:41.912211Z</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T22:00Z</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr"/>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
+      <c r="AB177" s="2" t="inlineStr"/>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr"/>
+      <c r="AE177" s="2" t="inlineStr"/>
+      <c r="AF177" s="2" t="inlineStr"/>
+      <c r="AG177" s="2" t="inlineStr"/>
+      <c r="AH177" s="2" t="inlineStr"/>
+      <c r="AI177" s="2" t="inlineStr"/>
+      <c r="AJ177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>cb5a35e2f10849a3</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181801</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>0.584559</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>0.04538849308755766</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:43.370610Z</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:00Z</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr"/>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr"/>
+      <c r="AB178" s="2" t="inlineStr"/>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr"/>
+      <c r="AE178" s="2" t="inlineStr"/>
+      <c r="AF178" s="2" t="inlineStr"/>
+      <c r="AG178" s="2" t="inlineStr"/>
+      <c r="AH178" s="2" t="inlineStr"/>
+      <c r="AI178" s="2" t="inlineStr"/>
+      <c r="AJ178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>b06213f687ec49ac</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181798</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>0.552246</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr"/>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>0.013075493087557621</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:45.470234Z</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:30Z</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
+      <c r="AB179" s="2" t="inlineStr"/>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr"/>
+      <c r="AE179" s="2" t="inlineStr"/>
+      <c r="AF179" s="2" t="inlineStr"/>
+      <c r="AG179" s="2" t="inlineStr"/>
+      <c r="AH179" s="2" t="inlineStr"/>
+      <c r="AI179" s="2" t="inlineStr"/>
+      <c r="AJ179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>743a5639c9e84698</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>1c05a3c4f76bde5de709ff6bb1937b3c4c67149c2ea621b7c90ca07898e048e8</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181839</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>0.57909</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>0.49019607843137253</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>0.08889392156862747</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:20:46.306688Z</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T00:30Z</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+      <c r="AB180" s="2" t="inlineStr"/>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr"/>
+      <c r="AE180" s="2" t="inlineStr"/>
+      <c r="AF180" s="2" t="inlineStr"/>
+      <c r="AG180" s="2" t="inlineStr"/>
+      <c r="AH180" s="2" t="inlineStr"/>
+      <c r="AI180" s="2" t="inlineStr"/>
+      <c r="AJ180" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ171"/>
+  <autoFilter ref="A1:AJ180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/model_ledgers/tennis-surface-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$458</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$461</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ458"/>
+  <dimension ref="A1:AJ461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -51146,8 +51146,326 @@
       <c r="AI458" s="2" t="inlineStr"/>
       <c r="AJ458" s="2" t="inlineStr"/>
     </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>6f8f152118224ef6</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182206</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J459" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K459" s="2" t="inlineStr"/>
+      <c r="L459" s="2" t="inlineStr">
+        <is>
+          <t>0.530694</t>
+        </is>
+      </c>
+      <c r="M459" s="2" t="inlineStr"/>
+      <c r="N459" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O459" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P459" s="2" t="inlineStr"/>
+      <c r="Q459" s="2" t="inlineStr">
+        <is>
+          <t>0.1905579455782313</t>
+        </is>
+      </c>
+      <c r="R459" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:48.985170Z</t>
+        </is>
+      </c>
+      <c r="S459" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T23:00Z</t>
+        </is>
+      </c>
+      <c r="T459" s="2" t="inlineStr"/>
+      <c r="U459" s="2" t="inlineStr"/>
+      <c r="V459" s="2" t="inlineStr"/>
+      <c r="W459" s="2" t="inlineStr"/>
+      <c r="X459" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y459" s="2" t="inlineStr"/>
+      <c r="Z459" s="2" t="inlineStr"/>
+      <c r="AA459" s="2" t="inlineStr"/>
+      <c r="AB459" s="2" t="inlineStr"/>
+      <c r="AC459" s="2" t="inlineStr"/>
+      <c r="AD459" s="2" t="inlineStr"/>
+      <c r="AE459" s="2" t="inlineStr"/>
+      <c r="AF459" s="2" t="inlineStr"/>
+      <c r="AG459" s="2" t="inlineStr"/>
+      <c r="AH459" s="2" t="inlineStr"/>
+      <c r="AI459" s="2" t="inlineStr"/>
+      <c r="AJ459" s="2" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>4ccf44755d744888</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181793</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J460" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K460" s="2" t="inlineStr"/>
+      <c r="L460" s="2" t="inlineStr">
+        <is>
+          <t>0.59108</t>
+        </is>
+      </c>
+      <c r="M460" s="2" t="inlineStr"/>
+      <c r="N460" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O460" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P460" s="2" t="inlineStr"/>
+      <c r="Q460" s="2" t="inlineStr">
+        <is>
+          <t>-0.09932247678018569</t>
+        </is>
+      </c>
+      <c r="R460" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:42:06.129741Z</t>
+        </is>
+      </c>
+      <c r="S460" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00Z</t>
+        </is>
+      </c>
+      <c r="T460" s="2" t="inlineStr"/>
+      <c r="U460" s="2" t="inlineStr"/>
+      <c r="V460" s="2" t="inlineStr"/>
+      <c r="W460" s="2" t="inlineStr"/>
+      <c r="X460" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y460" s="2" t="inlineStr"/>
+      <c r="Z460" s="2" t="inlineStr"/>
+      <c r="AA460" s="2" t="inlineStr"/>
+      <c r="AB460" s="2" t="inlineStr"/>
+      <c r="AC460" s="2" t="inlineStr"/>
+      <c r="AD460" s="2" t="inlineStr"/>
+      <c r="AE460" s="2" t="inlineStr"/>
+      <c r="AF460" s="2" t="inlineStr"/>
+      <c r="AG460" s="2" t="inlineStr"/>
+      <c r="AH460" s="2" t="inlineStr"/>
+      <c r="AI460" s="2" t="inlineStr"/>
+      <c r="AJ460" s="2" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>e7d0199815304eac</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181792</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K461" s="2" t="inlineStr"/>
+      <c r="L461" s="2" t="inlineStr">
+        <is>
+          <t>0.598983</t>
+        </is>
+      </c>
+      <c r="M461" s="2" t="inlineStr"/>
+      <c r="N461" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O461" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P461" s="2" t="inlineStr"/>
+      <c r="Q461" s="2" t="inlineStr">
+        <is>
+          <t>-0.060880945578231316</t>
+        </is>
+      </c>
+      <c r="R461" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:42:07.450465Z</t>
+        </is>
+      </c>
+      <c r="S461" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T23:30Z</t>
+        </is>
+      </c>
+      <c r="T461" s="2" t="inlineStr"/>
+      <c r="U461" s="2" t="inlineStr"/>
+      <c r="V461" s="2" t="inlineStr"/>
+      <c r="W461" s="2" t="inlineStr"/>
+      <c r="X461" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y461" s="2" t="inlineStr"/>
+      <c r="Z461" s="2" t="inlineStr"/>
+      <c r="AA461" s="2" t="inlineStr"/>
+      <c r="AB461" s="2" t="inlineStr"/>
+      <c r="AC461" s="2" t="inlineStr"/>
+      <c r="AD461" s="2" t="inlineStr"/>
+      <c r="AE461" s="2" t="inlineStr"/>
+      <c r="AF461" s="2" t="inlineStr"/>
+      <c r="AG461" s="2" t="inlineStr"/>
+      <c r="AH461" s="2" t="inlineStr"/>
+      <c r="AI461" s="2" t="inlineStr"/>
+      <c r="AJ461" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ458"/>
+  <autoFilter ref="A1:AJ461"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/tennis-surface-elo.xlsx
+++ b/data/model_ledgers/tennis-surface-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$461</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$491</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ461"/>
+  <dimension ref="A1:AJ491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -51464,8 +51464,3248 @@
       <c r="AI461" s="2" t="inlineStr"/>
       <c r="AJ461" s="2" t="inlineStr"/>
     </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>40847371471248b1</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:182206</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K462" s="2" t="inlineStr"/>
+      <c r="L462" s="2" t="inlineStr">
+        <is>
+          <t>0.530694</t>
+        </is>
+      </c>
+      <c r="M462" s="2" t="inlineStr"/>
+      <c r="N462" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O462" s="2" t="inlineStr">
+        <is>
+          <t>0.33003300330033003</t>
+        </is>
+      </c>
+      <c r="P462" s="2" t="inlineStr"/>
+      <c r="Q462" s="2" t="inlineStr">
+        <is>
+          <t>0.20066099669966997</t>
+        </is>
+      </c>
+      <c r="R462" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:16:29.324291Z</t>
+        </is>
+      </c>
+      <c r="S462" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T23:00Z</t>
+        </is>
+      </c>
+      <c r="T462" s="2" t="inlineStr"/>
+      <c r="U462" s="2" t="inlineStr"/>
+      <c r="V462" s="2" t="inlineStr"/>
+      <c r="W462" s="2" t="inlineStr"/>
+      <c r="X462" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y462" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z462" s="2" t="inlineStr">
+        <is>
+          <t>0.330000</t>
+        </is>
+      </c>
+      <c r="AA462" s="2" t="inlineStr">
+        <is>
+          <t>-0.000033</t>
+        </is>
+      </c>
+      <c r="AB462" s="2" t="inlineStr">
+        <is>
+          <t>-1.0000</t>
+        </is>
+      </c>
+      <c r="AC462" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:40.759243Z</t>
+        </is>
+      </c>
+      <c r="AD462" s="2" t="inlineStr"/>
+      <c r="AE462" s="2" t="inlineStr"/>
+      <c r="AF462" s="2" t="inlineStr"/>
+      <c r="AG462" s="2" t="inlineStr"/>
+      <c r="AH462" s="2" t="inlineStr"/>
+      <c r="AI462" s="2" t="inlineStr"/>
+      <c r="AJ462" s="2" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>a5e1cf539fd041ad</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181793</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K463" s="2" t="inlineStr"/>
+      <c r="L463" s="2" t="inlineStr">
+        <is>
+          <t>0.59108</t>
+        </is>
+      </c>
+      <c r="M463" s="2" t="inlineStr"/>
+      <c r="N463" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O463" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P463" s="2" t="inlineStr"/>
+      <c r="Q463" s="2" t="inlineStr">
+        <is>
+          <t>-0.10861969969969965</t>
+        </is>
+      </c>
+      <c r="R463" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:16:30.094408Z</t>
+        </is>
+      </c>
+      <c r="S463" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:00Z</t>
+        </is>
+      </c>
+      <c r="T463" s="2" t="inlineStr"/>
+      <c r="U463" s="2" t="inlineStr"/>
+      <c r="V463" s="2" t="inlineStr"/>
+      <c r="W463" s="2" t="inlineStr"/>
+      <c r="X463" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y463" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z463" s="2" t="inlineStr">
+        <is>
+          <t>0.700000</t>
+        </is>
+      </c>
+      <c r="AA463" s="2" t="inlineStr">
+        <is>
+          <t>0.000300</t>
+        </is>
+      </c>
+      <c r="AB463" s="2" t="inlineStr">
+        <is>
+          <t>-1.2500</t>
+        </is>
+      </c>
+      <c r="AC463" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:42.570546Z</t>
+        </is>
+      </c>
+      <c r="AD463" s="2" t="inlineStr"/>
+      <c r="AE463" s="2" t="inlineStr"/>
+      <c r="AF463" s="2" t="inlineStr"/>
+      <c r="AG463" s="2" t="inlineStr"/>
+      <c r="AH463" s="2" t="inlineStr"/>
+      <c r="AI463" s="2" t="inlineStr"/>
+      <c r="AJ463" s="2" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>0b17e658562b4755</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181792</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J464" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K464" s="2" t="inlineStr"/>
+      <c r="L464" s="2" t="inlineStr">
+        <is>
+          <t>0.598983</t>
+        </is>
+      </c>
+      <c r="M464" s="2" t="inlineStr"/>
+      <c r="N464" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O464" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P464" s="2" t="inlineStr"/>
+      <c r="Q464" s="2" t="inlineStr">
+        <is>
+          <t>-0.07098399669966993</t>
+        </is>
+      </c>
+      <c r="R464" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:16:31.426889Z</t>
+        </is>
+      </c>
+      <c r="S464" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T23:30Z</t>
+        </is>
+      </c>
+      <c r="T464" s="2" t="inlineStr"/>
+      <c r="U464" s="2" t="inlineStr"/>
+      <c r="V464" s="2" t="inlineStr"/>
+      <c r="W464" s="2" t="inlineStr"/>
+      <c r="X464" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y464" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z464" s="2" t="inlineStr">
+        <is>
+          <t>0.670000</t>
+        </is>
+      </c>
+      <c r="AA464" s="2" t="inlineStr">
+        <is>
+          <t>0.000033</t>
+        </is>
+      </c>
+      <c r="AB464" s="2" t="inlineStr">
+        <is>
+          <t>0.6158</t>
+        </is>
+      </c>
+      <c r="AC464" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:32:44.579293Z</t>
+        </is>
+      </c>
+      <c r="AD464" s="2" t="inlineStr"/>
+      <c r="AE464" s="2" t="inlineStr"/>
+      <c r="AF464" s="2" t="inlineStr"/>
+      <c r="AG464" s="2" t="inlineStr"/>
+      <c r="AH464" s="2" t="inlineStr"/>
+      <c r="AI464" s="2" t="inlineStr"/>
+      <c r="AJ464" s="2" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>35e64d45f57847de</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184471</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K465" s="2" t="inlineStr"/>
+      <c r="L465" s="2" t="inlineStr">
+        <is>
+          <t>0.511871</t>
+        </is>
+      </c>
+      <c r="M465" s="2" t="inlineStr"/>
+      <c r="N465" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O465" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P465" s="2" t="inlineStr"/>
+      <c r="Q465" s="2" t="inlineStr">
+        <is>
+          <t>-0.06796093277310922</t>
+        </is>
+      </c>
+      <c r="R465" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:36:00.154819Z</t>
+        </is>
+      </c>
+      <c r="S465" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T465" s="2" t="inlineStr"/>
+      <c r="U465" s="2" t="inlineStr"/>
+      <c r="V465" s="2" t="inlineStr"/>
+      <c r="W465" s="2" t="inlineStr"/>
+      <c r="X465" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y465" s="2" t="inlineStr"/>
+      <c r="Z465" s="2" t="inlineStr"/>
+      <c r="AA465" s="2" t="inlineStr"/>
+      <c r="AB465" s="2" t="inlineStr"/>
+      <c r="AC465" s="2" t="inlineStr"/>
+      <c r="AD465" s="2" t="inlineStr"/>
+      <c r="AE465" s="2" t="inlineStr"/>
+      <c r="AF465" s="2" t="inlineStr"/>
+      <c r="AG465" s="2" t="inlineStr"/>
+      <c r="AH465" s="2" t="inlineStr"/>
+      <c r="AI465" s="2" t="inlineStr"/>
+      <c r="AJ465" s="2" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>bcd7537941d640b8</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184475</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J466" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K466" s="2" t="inlineStr"/>
+      <c r="L466" s="2" t="inlineStr">
+        <is>
+          <t>0.571683</t>
+        </is>
+      </c>
+      <c r="M466" s="2" t="inlineStr"/>
+      <c r="N466" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O466" s="2" t="inlineStr">
+        <is>
+          <t>0.44052863436123346</t>
+        </is>
+      </c>
+      <c r="P466" s="2" t="inlineStr"/>
+      <c r="Q466" s="2" t="inlineStr">
+        <is>
+          <t>0.1311543656387666</t>
+        </is>
+      </c>
+      <c r="R466" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:36:00.621269Z</t>
+        </is>
+      </c>
+      <c r="S466" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T466" s="2" t="inlineStr"/>
+      <c r="U466" s="2" t="inlineStr"/>
+      <c r="V466" s="2" t="inlineStr"/>
+      <c r="W466" s="2" t="inlineStr"/>
+      <c r="X466" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y466" s="2" t="inlineStr"/>
+      <c r="Z466" s="2" t="inlineStr"/>
+      <c r="AA466" s="2" t="inlineStr"/>
+      <c r="AB466" s="2" t="inlineStr"/>
+      <c r="AC466" s="2" t="inlineStr"/>
+      <c r="AD466" s="2" t="inlineStr"/>
+      <c r="AE466" s="2" t="inlineStr"/>
+      <c r="AF466" s="2" t="inlineStr"/>
+      <c r="AG466" s="2" t="inlineStr"/>
+      <c r="AH466" s="2" t="inlineStr"/>
+      <c r="AI466" s="2" t="inlineStr"/>
+      <c r="AJ466" s="2" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>7a734b7699874a04</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181845</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K467" s="2" t="inlineStr"/>
+      <c r="L467" s="2" t="inlineStr">
+        <is>
+          <t>0.706772</t>
+        </is>
+      </c>
+      <c r="M467" s="2" t="inlineStr"/>
+      <c r="N467" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O467" s="2" t="inlineStr">
+        <is>
+          <t>0.66996699669967</t>
+        </is>
+      </c>
+      <c r="P467" s="2" t="inlineStr"/>
+      <c r="Q467" s="2" t="inlineStr">
+        <is>
+          <t>0.036805003300329986</t>
+        </is>
+      </c>
+      <c r="R467" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:36:19.835538Z</t>
+        </is>
+      </c>
+      <c r="S467" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00Z</t>
+        </is>
+      </c>
+      <c r="T467" s="2" t="inlineStr"/>
+      <c r="U467" s="2" t="inlineStr"/>
+      <c r="V467" s="2" t="inlineStr"/>
+      <c r="W467" s="2" t="inlineStr"/>
+      <c r="X467" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y467" s="2" t="inlineStr"/>
+      <c r="Z467" s="2" t="inlineStr"/>
+      <c r="AA467" s="2" t="inlineStr"/>
+      <c r="AB467" s="2" t="inlineStr"/>
+      <c r="AC467" s="2" t="inlineStr"/>
+      <c r="AD467" s="2" t="inlineStr"/>
+      <c r="AE467" s="2" t="inlineStr"/>
+      <c r="AF467" s="2" t="inlineStr"/>
+      <c r="AG467" s="2" t="inlineStr"/>
+      <c r="AH467" s="2" t="inlineStr"/>
+      <c r="AI467" s="2" t="inlineStr"/>
+      <c r="AJ467" s="2" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>272def2b3a614040</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184432</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K468" s="2" t="inlineStr"/>
+      <c r="L468" s="2" t="inlineStr">
+        <is>
+          <t>0.560751</t>
+        </is>
+      </c>
+      <c r="M468" s="2" t="inlineStr"/>
+      <c r="N468" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O468" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P468" s="2" t="inlineStr"/>
+      <c r="Q468" s="2" t="inlineStr">
+        <is>
+          <t>-0.1389486996996997</t>
+        </is>
+      </c>
+      <c r="R468" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:36:19.032732Z</t>
+        </is>
+      </c>
+      <c r="S468" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T468" s="2" t="inlineStr"/>
+      <c r="U468" s="2" t="inlineStr"/>
+      <c r="V468" s="2" t="inlineStr"/>
+      <c r="W468" s="2" t="inlineStr"/>
+      <c r="X468" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y468" s="2" t="inlineStr"/>
+      <c r="Z468" s="2" t="inlineStr"/>
+      <c r="AA468" s="2" t="inlineStr"/>
+      <c r="AB468" s="2" t="inlineStr"/>
+      <c r="AC468" s="2" t="inlineStr"/>
+      <c r="AD468" s="2" t="inlineStr"/>
+      <c r="AE468" s="2" t="inlineStr"/>
+      <c r="AF468" s="2" t="inlineStr"/>
+      <c r="AG468" s="2" t="inlineStr"/>
+      <c r="AH468" s="2" t="inlineStr"/>
+      <c r="AI468" s="2" t="inlineStr"/>
+      <c r="AJ468" s="2" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>fa99e759fab948e4</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184442</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J469" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K469" s="2" t="inlineStr"/>
+      <c r="L469" s="2" t="inlineStr">
+        <is>
+          <t>0.514136</t>
+        </is>
+      </c>
+      <c r="M469" s="2" t="inlineStr"/>
+      <c r="N469" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O469" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P469" s="2" t="inlineStr"/>
+      <c r="Q469" s="2" t="inlineStr">
+        <is>
+          <t>-0.10563586311787065</t>
+        </is>
+      </c>
+      <c r="R469" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:36:19.707318Z</t>
+        </is>
+      </c>
+      <c r="S469" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T469" s="2" t="inlineStr"/>
+      <c r="U469" s="2" t="inlineStr"/>
+      <c r="V469" s="2" t="inlineStr"/>
+      <c r="W469" s="2" t="inlineStr"/>
+      <c r="X469" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y469" s="2" t="inlineStr"/>
+      <c r="Z469" s="2" t="inlineStr"/>
+      <c r="AA469" s="2" t="inlineStr"/>
+      <c r="AB469" s="2" t="inlineStr"/>
+      <c r="AC469" s="2" t="inlineStr"/>
+      <c r="AD469" s="2" t="inlineStr"/>
+      <c r="AE469" s="2" t="inlineStr"/>
+      <c r="AF469" s="2" t="inlineStr"/>
+      <c r="AG469" s="2" t="inlineStr"/>
+      <c r="AH469" s="2" t="inlineStr"/>
+      <c r="AI469" s="2" t="inlineStr"/>
+      <c r="AJ469" s="2" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>f3b6ff8aefb04ac2</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184471</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K470" s="2" t="inlineStr"/>
+      <c r="L470" s="2" t="inlineStr">
+        <is>
+          <t>0.511871</t>
+        </is>
+      </c>
+      <c r="M470" s="2" t="inlineStr"/>
+      <c r="N470" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O470" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P470" s="2" t="inlineStr"/>
+      <c r="Q470" s="2" t="inlineStr">
+        <is>
+          <t>-0.07829293442622953</t>
+        </is>
+      </c>
+      <c r="R470" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:31.522282Z</t>
+        </is>
+      </c>
+      <c r="S470" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T470" s="2" t="inlineStr"/>
+      <c r="U470" s="2" t="inlineStr"/>
+      <c r="V470" s="2" t="inlineStr"/>
+      <c r="W470" s="2" t="inlineStr"/>
+      <c r="X470" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y470" s="2" t="inlineStr"/>
+      <c r="Z470" s="2" t="inlineStr"/>
+      <c r="AA470" s="2" t="inlineStr"/>
+      <c r="AB470" s="2" t="inlineStr"/>
+      <c r="AC470" s="2" t="inlineStr"/>
+      <c r="AD470" s="2" t="inlineStr"/>
+      <c r="AE470" s="2" t="inlineStr"/>
+      <c r="AF470" s="2" t="inlineStr"/>
+      <c r="AG470" s="2" t="inlineStr"/>
+      <c r="AH470" s="2" t="inlineStr"/>
+      <c r="AI470" s="2" t="inlineStr"/>
+      <c r="AJ470" s="2" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>9f807842c8684639</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184475</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J471" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K471" s="2" t="inlineStr"/>
+      <c r="L471" s="2" t="inlineStr">
+        <is>
+          <t>0.571683</t>
+        </is>
+      </c>
+      <c r="M471" s="2" t="inlineStr"/>
+      <c r="N471" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O471" s="2" t="inlineStr">
+        <is>
+          <t>0.3205128205128205</t>
+        </is>
+      </c>
+      <c r="P471" s="2" t="inlineStr"/>
+      <c r="Q471" s="2" t="inlineStr">
+        <is>
+          <t>0.25117017948717957</t>
+        </is>
+      </c>
+      <c r="R471" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:32.042774Z</t>
+        </is>
+      </c>
+      <c r="S471" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T471" s="2" t="inlineStr"/>
+      <c r="U471" s="2" t="inlineStr"/>
+      <c r="V471" s="2" t="inlineStr"/>
+      <c r="W471" s="2" t="inlineStr"/>
+      <c r="X471" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y471" s="2" t="inlineStr"/>
+      <c r="Z471" s="2" t="inlineStr"/>
+      <c r="AA471" s="2" t="inlineStr"/>
+      <c r="AB471" s="2" t="inlineStr"/>
+      <c r="AC471" s="2" t="inlineStr"/>
+      <c r="AD471" s="2" t="inlineStr"/>
+      <c r="AE471" s="2" t="inlineStr"/>
+      <c r="AF471" s="2" t="inlineStr"/>
+      <c r="AG471" s="2" t="inlineStr"/>
+      <c r="AH471" s="2" t="inlineStr"/>
+      <c r="AI471" s="2" t="inlineStr"/>
+      <c r="AJ471" s="2" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>70a2d17cc3944c58</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181845</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J472" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K472" s="2" t="inlineStr"/>
+      <c r="L472" s="2" t="inlineStr">
+        <is>
+          <t>0.706772</t>
+        </is>
+      </c>
+      <c r="M472" s="2" t="inlineStr"/>
+      <c r="N472" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O472" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P472" s="2" t="inlineStr"/>
+      <c r="Q472" s="2" t="inlineStr">
+        <is>
+          <t>0.01636952321981422</t>
+        </is>
+      </c>
+      <c r="R472" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:54.244331Z</t>
+        </is>
+      </c>
+      <c r="S472" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00Z</t>
+        </is>
+      </c>
+      <c r="T472" s="2" t="inlineStr"/>
+      <c r="U472" s="2" t="inlineStr"/>
+      <c r="V472" s="2" t="inlineStr"/>
+      <c r="W472" s="2" t="inlineStr"/>
+      <c r="X472" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y472" s="2" t="inlineStr"/>
+      <c r="Z472" s="2" t="inlineStr"/>
+      <c r="AA472" s="2" t="inlineStr"/>
+      <c r="AB472" s="2" t="inlineStr"/>
+      <c r="AC472" s="2" t="inlineStr"/>
+      <c r="AD472" s="2" t="inlineStr"/>
+      <c r="AE472" s="2" t="inlineStr"/>
+      <c r="AF472" s="2" t="inlineStr"/>
+      <c r="AG472" s="2" t="inlineStr"/>
+      <c r="AH472" s="2" t="inlineStr"/>
+      <c r="AI472" s="2" t="inlineStr"/>
+      <c r="AJ472" s="2" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>e914d93b2dfe4c3d</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184432</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J473" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K473" s="2" t="inlineStr"/>
+      <c r="L473" s="2" t="inlineStr">
+        <is>
+          <t>0.560751</t>
+        </is>
+      </c>
+      <c r="M473" s="2" t="inlineStr"/>
+      <c r="N473" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O473" s="2" t="inlineStr">
+        <is>
+          <t>0.9300209937018894</t>
+        </is>
+      </c>
+      <c r="P473" s="2" t="inlineStr"/>
+      <c r="Q473" s="2" t="inlineStr">
+        <is>
+          <t>-0.3692699937018894</t>
+        </is>
+      </c>
+      <c r="R473" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:52.872709Z</t>
+        </is>
+      </c>
+      <c r="S473" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T473" s="2" t="inlineStr"/>
+      <c r="U473" s="2" t="inlineStr"/>
+      <c r="V473" s="2" t="inlineStr"/>
+      <c r="W473" s="2" t="inlineStr"/>
+      <c r="X473" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y473" s="2" t="inlineStr"/>
+      <c r="Z473" s="2" t="inlineStr"/>
+      <c r="AA473" s="2" t="inlineStr"/>
+      <c r="AB473" s="2" t="inlineStr"/>
+      <c r="AC473" s="2" t="inlineStr"/>
+      <c r="AD473" s="2" t="inlineStr"/>
+      <c r="AE473" s="2" t="inlineStr"/>
+      <c r="AF473" s="2" t="inlineStr"/>
+      <c r="AG473" s="2" t="inlineStr"/>
+      <c r="AH473" s="2" t="inlineStr"/>
+      <c r="AI473" s="2" t="inlineStr"/>
+      <c r="AJ473" s="2" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>947d5987b85d4e1f</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184442</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J474" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K474" s="2" t="inlineStr"/>
+      <c r="L474" s="2" t="inlineStr">
+        <is>
+          <t>0.514136</t>
+        </is>
+      </c>
+      <c r="M474" s="2" t="inlineStr"/>
+      <c r="N474" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O474" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P474" s="2" t="inlineStr"/>
+      <c r="Q474" s="2" t="inlineStr">
+        <is>
+          <t>-0.06569593277310914</t>
+        </is>
+      </c>
+      <c r="R474" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:30:53.722489Z</t>
+        </is>
+      </c>
+      <c r="S474" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T474" s="2" t="inlineStr"/>
+      <c r="U474" s="2" t="inlineStr"/>
+      <c r="V474" s="2" t="inlineStr"/>
+      <c r="W474" s="2" t="inlineStr"/>
+      <c r="X474" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y474" s="2" t="inlineStr"/>
+      <c r="Z474" s="2" t="inlineStr"/>
+      <c r="AA474" s="2" t="inlineStr"/>
+      <c r="AB474" s="2" t="inlineStr"/>
+      <c r="AC474" s="2" t="inlineStr"/>
+      <c r="AD474" s="2" t="inlineStr"/>
+      <c r="AE474" s="2" t="inlineStr"/>
+      <c r="AF474" s="2" t="inlineStr"/>
+      <c r="AG474" s="2" t="inlineStr"/>
+      <c r="AH474" s="2" t="inlineStr"/>
+      <c r="AI474" s="2" t="inlineStr"/>
+      <c r="AJ474" s="2" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>f2594cd6e73d4581</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184471</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K475" s="2" t="inlineStr"/>
+      <c r="L475" s="2" t="inlineStr">
+        <is>
+          <t>0.511871</t>
+        </is>
+      </c>
+      <c r="M475" s="2" t="inlineStr"/>
+      <c r="N475" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O475" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P475" s="2" t="inlineStr"/>
+      <c r="Q475" s="2" t="inlineStr">
+        <is>
+          <t>-0.08812900000000012</t>
+        </is>
+      </c>
+      <c r="R475" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:08:02.990405Z</t>
+        </is>
+      </c>
+      <c r="S475" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T475" s="2" t="inlineStr"/>
+      <c r="U475" s="2" t="inlineStr"/>
+      <c r="V475" s="2" t="inlineStr"/>
+      <c r="W475" s="2" t="inlineStr"/>
+      <c r="X475" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y475" s="2" t="inlineStr"/>
+      <c r="Z475" s="2" t="inlineStr"/>
+      <c r="AA475" s="2" t="inlineStr"/>
+      <c r="AB475" s="2" t="inlineStr"/>
+      <c r="AC475" s="2" t="inlineStr"/>
+      <c r="AD475" s="2" t="inlineStr"/>
+      <c r="AE475" s="2" t="inlineStr"/>
+      <c r="AF475" s="2" t="inlineStr"/>
+      <c r="AG475" s="2" t="inlineStr"/>
+      <c r="AH475" s="2" t="inlineStr"/>
+      <c r="AI475" s="2" t="inlineStr"/>
+      <c r="AJ475" s="2" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>a6eae480a59a4b96</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184475</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K476" s="2" t="inlineStr"/>
+      <c r="L476" s="2" t="inlineStr">
+        <is>
+          <t>0.571683</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="inlineStr"/>
+      <c r="N476" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O476" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P476" s="2" t="inlineStr"/>
+      <c r="Q476" s="2" t="inlineStr">
+        <is>
+          <t>0.17168300000000003</t>
+        </is>
+      </c>
+      <c r="R476" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:08:03.516653Z</t>
+        </is>
+      </c>
+      <c r="S476" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T476" s="2" t="inlineStr"/>
+      <c r="U476" s="2" t="inlineStr"/>
+      <c r="V476" s="2" t="inlineStr"/>
+      <c r="W476" s="2" t="inlineStr"/>
+      <c r="X476" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y476" s="2" t="inlineStr"/>
+      <c r="Z476" s="2" t="inlineStr"/>
+      <c r="AA476" s="2" t="inlineStr"/>
+      <c r="AB476" s="2" t="inlineStr"/>
+      <c r="AC476" s="2" t="inlineStr"/>
+      <c r="AD476" s="2" t="inlineStr"/>
+      <c r="AE476" s="2" t="inlineStr"/>
+      <c r="AF476" s="2" t="inlineStr"/>
+      <c r="AG476" s="2" t="inlineStr"/>
+      <c r="AH476" s="2" t="inlineStr"/>
+      <c r="AI476" s="2" t="inlineStr"/>
+      <c r="AJ476" s="2" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>c52eb5216c2b4683</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181845</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K477" s="2" t="inlineStr"/>
+      <c r="L477" s="2" t="inlineStr">
+        <is>
+          <t>0.706772</t>
+        </is>
+      </c>
+      <c r="M477" s="2" t="inlineStr"/>
+      <c r="N477" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O477" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P477" s="2" t="inlineStr"/>
+      <c r="Q477" s="2" t="inlineStr">
+        <is>
+          <t>0.0262608178913738</t>
+        </is>
+      </c>
+      <c r="R477" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:08:22.220845Z</t>
+        </is>
+      </c>
+      <c r="S477" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00Z</t>
+        </is>
+      </c>
+      <c r="T477" s="2" t="inlineStr"/>
+      <c r="U477" s="2" t="inlineStr"/>
+      <c r="V477" s="2" t="inlineStr"/>
+      <c r="W477" s="2" t="inlineStr"/>
+      <c r="X477" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y477" s="2" t="inlineStr"/>
+      <c r="Z477" s="2" t="inlineStr"/>
+      <c r="AA477" s="2" t="inlineStr"/>
+      <c r="AB477" s="2" t="inlineStr"/>
+      <c r="AC477" s="2" t="inlineStr"/>
+      <c r="AD477" s="2" t="inlineStr"/>
+      <c r="AE477" s="2" t="inlineStr"/>
+      <c r="AF477" s="2" t="inlineStr"/>
+      <c r="AG477" s="2" t="inlineStr"/>
+      <c r="AH477" s="2" t="inlineStr"/>
+      <c r="AI477" s="2" t="inlineStr"/>
+      <c r="AJ477" s="2" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>1d814e132b534895</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184432</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K478" s="2" t="inlineStr"/>
+      <c r="L478" s="2" t="inlineStr">
+        <is>
+          <t>0.560751</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="inlineStr"/>
+      <c r="N478" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O478" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P478" s="2" t="inlineStr"/>
+      <c r="Q478" s="2" t="inlineStr">
+        <is>
+          <t>-0.019080932773109183</t>
+        </is>
+      </c>
+      <c r="R478" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:08:20.818631Z</t>
+        </is>
+      </c>
+      <c r="S478" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T478" s="2" t="inlineStr"/>
+      <c r="U478" s="2" t="inlineStr"/>
+      <c r="V478" s="2" t="inlineStr"/>
+      <c r="W478" s="2" t="inlineStr"/>
+      <c r="X478" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y478" s="2" t="inlineStr"/>
+      <c r="Z478" s="2" t="inlineStr"/>
+      <c r="AA478" s="2" t="inlineStr"/>
+      <c r="AB478" s="2" t="inlineStr"/>
+      <c r="AC478" s="2" t="inlineStr"/>
+      <c r="AD478" s="2" t="inlineStr"/>
+      <c r="AE478" s="2" t="inlineStr"/>
+      <c r="AF478" s="2" t="inlineStr"/>
+      <c r="AG478" s="2" t="inlineStr"/>
+      <c r="AH478" s="2" t="inlineStr"/>
+      <c r="AI478" s="2" t="inlineStr"/>
+      <c r="AJ478" s="2" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>f4dfab2dbda64741</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184442</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J479" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K479" s="2" t="inlineStr"/>
+      <c r="L479" s="2" t="inlineStr">
+        <is>
+          <t>0.514136</t>
+        </is>
+      </c>
+      <c r="M479" s="2" t="inlineStr"/>
+      <c r="N479" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O479" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P479" s="2" t="inlineStr"/>
+      <c r="Q479" s="2" t="inlineStr">
+        <is>
+          <t>-0.0453353656387665</t>
+        </is>
+      </c>
+      <c r="R479" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:08:21.626055Z</t>
+        </is>
+      </c>
+      <c r="S479" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T479" s="2" t="inlineStr"/>
+      <c r="U479" s="2" t="inlineStr"/>
+      <c r="V479" s="2" t="inlineStr"/>
+      <c r="W479" s="2" t="inlineStr"/>
+      <c r="X479" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y479" s="2" t="inlineStr"/>
+      <c r="Z479" s="2" t="inlineStr"/>
+      <c r="AA479" s="2" t="inlineStr"/>
+      <c r="AB479" s="2" t="inlineStr"/>
+      <c r="AC479" s="2" t="inlineStr"/>
+      <c r="AD479" s="2" t="inlineStr"/>
+      <c r="AE479" s="2" t="inlineStr"/>
+      <c r="AF479" s="2" t="inlineStr"/>
+      <c r="AG479" s="2" t="inlineStr"/>
+      <c r="AH479" s="2" t="inlineStr"/>
+      <c r="AI479" s="2" t="inlineStr"/>
+      <c r="AJ479" s="2" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>0a11bd187a4f4404</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184471</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J480" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K480" s="2" t="inlineStr"/>
+      <c r="L480" s="2" t="inlineStr">
+        <is>
+          <t>0.511871</t>
+        </is>
+      </c>
+      <c r="M480" s="2" t="inlineStr"/>
+      <c r="N480" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O480" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P480" s="2" t="inlineStr"/>
+      <c r="Q480" s="2" t="inlineStr">
+        <is>
+          <t>-0.08812900000000012</t>
+        </is>
+      </c>
+      <c r="R480" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:26.572402Z</t>
+        </is>
+      </c>
+      <c r="S480" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T480" s="2" t="inlineStr"/>
+      <c r="U480" s="2" t="inlineStr"/>
+      <c r="V480" s="2" t="inlineStr"/>
+      <c r="W480" s="2" t="inlineStr"/>
+      <c r="X480" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y480" s="2" t="inlineStr"/>
+      <c r="Z480" s="2" t="inlineStr"/>
+      <c r="AA480" s="2" t="inlineStr"/>
+      <c r="AB480" s="2" t="inlineStr"/>
+      <c r="AC480" s="2" t="inlineStr"/>
+      <c r="AD480" s="2" t="inlineStr"/>
+      <c r="AE480" s="2" t="inlineStr"/>
+      <c r="AF480" s="2" t="inlineStr"/>
+      <c r="AG480" s="2" t="inlineStr"/>
+      <c r="AH480" s="2" t="inlineStr"/>
+      <c r="AI480" s="2" t="inlineStr"/>
+      <c r="AJ480" s="2" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>c0064080f23a46a9</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184475</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J481" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K481" s="2" t="inlineStr"/>
+      <c r="L481" s="2" t="inlineStr">
+        <is>
+          <t>0.571683</t>
+        </is>
+      </c>
+      <c r="M481" s="2" t="inlineStr"/>
+      <c r="N481" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O481" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P481" s="2" t="inlineStr"/>
+      <c r="Q481" s="2" t="inlineStr">
+        <is>
+          <t>0.17168300000000003</t>
+        </is>
+      </c>
+      <c r="R481" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:27.238937Z</t>
+        </is>
+      </c>
+      <c r="S481" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T481" s="2" t="inlineStr"/>
+      <c r="U481" s="2" t="inlineStr"/>
+      <c r="V481" s="2" t="inlineStr"/>
+      <c r="W481" s="2" t="inlineStr"/>
+      <c r="X481" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y481" s="2" t="inlineStr"/>
+      <c r="Z481" s="2" t="inlineStr"/>
+      <c r="AA481" s="2" t="inlineStr"/>
+      <c r="AB481" s="2" t="inlineStr"/>
+      <c r="AC481" s="2" t="inlineStr"/>
+      <c r="AD481" s="2" t="inlineStr"/>
+      <c r="AE481" s="2" t="inlineStr"/>
+      <c r="AF481" s="2" t="inlineStr"/>
+      <c r="AG481" s="2" t="inlineStr"/>
+      <c r="AH481" s="2" t="inlineStr"/>
+      <c r="AI481" s="2" t="inlineStr"/>
+      <c r="AJ481" s="2" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>bb23ecb861924b72</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181845</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J482" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K482" s="2" t="inlineStr"/>
+      <c r="L482" s="2" t="inlineStr">
+        <is>
+          <t>0.706772</t>
+        </is>
+      </c>
+      <c r="M482" s="2" t="inlineStr"/>
+      <c r="N482" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O482" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P482" s="2" t="inlineStr"/>
+      <c r="Q482" s="2" t="inlineStr">
+        <is>
+          <t>0.0262608178913738</t>
+        </is>
+      </c>
+      <c r="R482" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:46.094361Z</t>
+        </is>
+      </c>
+      <c r="S482" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00Z</t>
+        </is>
+      </c>
+      <c r="T482" s="2" t="inlineStr"/>
+      <c r="U482" s="2" t="inlineStr"/>
+      <c r="V482" s="2" t="inlineStr"/>
+      <c r="W482" s="2" t="inlineStr"/>
+      <c r="X482" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y482" s="2" t="inlineStr"/>
+      <c r="Z482" s="2" t="inlineStr"/>
+      <c r="AA482" s="2" t="inlineStr"/>
+      <c r="AB482" s="2" t="inlineStr"/>
+      <c r="AC482" s="2" t="inlineStr"/>
+      <c r="AD482" s="2" t="inlineStr"/>
+      <c r="AE482" s="2" t="inlineStr"/>
+      <c r="AF482" s="2" t="inlineStr"/>
+      <c r="AG482" s="2" t="inlineStr"/>
+      <c r="AH482" s="2" t="inlineStr"/>
+      <c r="AI482" s="2" t="inlineStr"/>
+      <c r="AJ482" s="2" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>1f65f11ca6a24aa6</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184432</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K483" s="2" t="inlineStr"/>
+      <c r="L483" s="2" t="inlineStr">
+        <is>
+          <t>0.560751</t>
+        </is>
+      </c>
+      <c r="M483" s="2" t="inlineStr"/>
+      <c r="N483" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O483" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P483" s="2" t="inlineStr"/>
+      <c r="Q483" s="2" t="inlineStr">
+        <is>
+          <t>-0.019080932773109183</t>
+        </is>
+      </c>
+      <c r="R483" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:44.639259Z</t>
+        </is>
+      </c>
+      <c r="S483" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T483" s="2" t="inlineStr"/>
+      <c r="U483" s="2" t="inlineStr"/>
+      <c r="V483" s="2" t="inlineStr"/>
+      <c r="W483" s="2" t="inlineStr"/>
+      <c r="X483" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y483" s="2" t="inlineStr"/>
+      <c r="Z483" s="2" t="inlineStr"/>
+      <c r="AA483" s="2" t="inlineStr"/>
+      <c r="AB483" s="2" t="inlineStr"/>
+      <c r="AC483" s="2" t="inlineStr"/>
+      <c r="AD483" s="2" t="inlineStr"/>
+      <c r="AE483" s="2" t="inlineStr"/>
+      <c r="AF483" s="2" t="inlineStr"/>
+      <c r="AG483" s="2" t="inlineStr"/>
+      <c r="AH483" s="2" t="inlineStr"/>
+      <c r="AI483" s="2" t="inlineStr"/>
+      <c r="AJ483" s="2" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>3adbaf972ae44c72</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184442</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J484" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K484" s="2" t="inlineStr"/>
+      <c r="L484" s="2" t="inlineStr">
+        <is>
+          <t>0.514136</t>
+        </is>
+      </c>
+      <c r="M484" s="2" t="inlineStr"/>
+      <c r="N484" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O484" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P484" s="2" t="inlineStr"/>
+      <c r="Q484" s="2" t="inlineStr">
+        <is>
+          <t>-0.0453353656387665</t>
+        </is>
+      </c>
+      <c r="R484" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:37:45.505769Z</t>
+        </is>
+      </c>
+      <c r="S484" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T484" s="2" t="inlineStr"/>
+      <c r="U484" s="2" t="inlineStr"/>
+      <c r="V484" s="2" t="inlineStr"/>
+      <c r="W484" s="2" t="inlineStr"/>
+      <c r="X484" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y484" s="2" t="inlineStr"/>
+      <c r="Z484" s="2" t="inlineStr"/>
+      <c r="AA484" s="2" t="inlineStr"/>
+      <c r="AB484" s="2" t="inlineStr"/>
+      <c r="AC484" s="2" t="inlineStr"/>
+      <c r="AD484" s="2" t="inlineStr"/>
+      <c r="AE484" s="2" t="inlineStr"/>
+      <c r="AF484" s="2" t="inlineStr"/>
+      <c r="AG484" s="2" t="inlineStr"/>
+      <c r="AH484" s="2" t="inlineStr"/>
+      <c r="AI484" s="2" t="inlineStr"/>
+      <c r="AJ484" s="2" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>821ab52b65fd4bc9</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184471</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J485" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K485" s="2" t="inlineStr"/>
+      <c r="L485" s="2" t="inlineStr">
+        <is>
+          <t>0.50026</t>
+        </is>
+      </c>
+      <c r="M485" s="2" t="inlineStr"/>
+      <c r="N485" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O485" s="2" t="inlineStr">
+        <is>
+          <t>0.4098360655737705</t>
+        </is>
+      </c>
+      <c r="P485" s="2" t="inlineStr"/>
+      <c r="Q485" s="2" t="inlineStr">
+        <is>
+          <t>0.09042393442622954</t>
+        </is>
+      </c>
+      <c r="R485" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:35.484534Z</t>
+        </is>
+      </c>
+      <c r="S485" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T485" s="2" t="inlineStr"/>
+      <c r="U485" s="2" t="inlineStr"/>
+      <c r="V485" s="2" t="inlineStr"/>
+      <c r="W485" s="2" t="inlineStr"/>
+      <c r="X485" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y485" s="2" t="inlineStr"/>
+      <c r="Z485" s="2" t="inlineStr"/>
+      <c r="AA485" s="2" t="inlineStr"/>
+      <c r="AB485" s="2" t="inlineStr"/>
+      <c r="AC485" s="2" t="inlineStr"/>
+      <c r="AD485" s="2" t="inlineStr"/>
+      <c r="AE485" s="2" t="inlineStr"/>
+      <c r="AF485" s="2" t="inlineStr"/>
+      <c r="AG485" s="2" t="inlineStr"/>
+      <c r="AH485" s="2" t="inlineStr"/>
+      <c r="AI485" s="2" t="inlineStr"/>
+      <c r="AJ485" s="2" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>75d059d678804d3a</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184475</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J486" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K486" s="2" t="inlineStr"/>
+      <c r="L486" s="2" t="inlineStr">
+        <is>
+          <t>0.57778</t>
+        </is>
+      </c>
+      <c r="M486" s="2" t="inlineStr"/>
+      <c r="N486" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O486" s="2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="P486" s="2" t="inlineStr"/>
+      <c r="Q486" s="2" t="inlineStr">
+        <is>
+          <t>0.17777999999999994</t>
+        </is>
+      </c>
+      <c r="R486" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:36.206620Z</t>
+        </is>
+      </c>
+      <c r="S486" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T486" s="2" t="inlineStr"/>
+      <c r="U486" s="2" t="inlineStr"/>
+      <c r="V486" s="2" t="inlineStr"/>
+      <c r="W486" s="2" t="inlineStr"/>
+      <c r="X486" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y486" s="2" t="inlineStr"/>
+      <c r="Z486" s="2" t="inlineStr"/>
+      <c r="AA486" s="2" t="inlineStr"/>
+      <c r="AB486" s="2" t="inlineStr"/>
+      <c r="AC486" s="2" t="inlineStr"/>
+      <c r="AD486" s="2" t="inlineStr"/>
+      <c r="AE486" s="2" t="inlineStr"/>
+      <c r="AF486" s="2" t="inlineStr"/>
+      <c r="AG486" s="2" t="inlineStr"/>
+      <c r="AH486" s="2" t="inlineStr"/>
+      <c r="AI486" s="2" t="inlineStr"/>
+      <c r="AJ486" s="2" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>a6e2c147d4734332</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181845</t>
+        </is>
+      </c>
+      <c r="I487" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J487" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K487" s="2" t="inlineStr"/>
+      <c r="L487" s="2" t="inlineStr">
+        <is>
+          <t>0.68139</t>
+        </is>
+      </c>
+      <c r="M487" s="2" t="inlineStr"/>
+      <c r="N487" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O487" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P487" s="2" t="inlineStr"/>
+      <c r="Q487" s="2" t="inlineStr">
+        <is>
+          <t>0.0008788178913738953</t>
+        </is>
+      </c>
+      <c r="R487" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:56.109125Z</t>
+        </is>
+      </c>
+      <c r="S487" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00Z</t>
+        </is>
+      </c>
+      <c r="T487" s="2" t="inlineStr"/>
+      <c r="U487" s="2" t="inlineStr"/>
+      <c r="V487" s="2" t="inlineStr"/>
+      <c r="W487" s="2" t="inlineStr"/>
+      <c r="X487" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y487" s="2" t="inlineStr"/>
+      <c r="Z487" s="2" t="inlineStr"/>
+      <c r="AA487" s="2" t="inlineStr"/>
+      <c r="AB487" s="2" t="inlineStr"/>
+      <c r="AC487" s="2" t="inlineStr"/>
+      <c r="AD487" s="2" t="inlineStr"/>
+      <c r="AE487" s="2" t="inlineStr"/>
+      <c r="AF487" s="2" t="inlineStr"/>
+      <c r="AG487" s="2" t="inlineStr"/>
+      <c r="AH487" s="2" t="inlineStr"/>
+      <c r="AI487" s="2" t="inlineStr"/>
+      <c r="AJ487" s="2" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>d7cf3e27e2334476</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184432</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J488" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K488" s="2" t="inlineStr"/>
+      <c r="L488" s="2" t="inlineStr">
+        <is>
+          <t>0.502184</t>
+        </is>
+      </c>
+      <c r="M488" s="2" t="inlineStr"/>
+      <c r="N488" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O488" s="2" t="inlineStr">
+        <is>
+          <t>0.4291845493562232</t>
+        </is>
+      </c>
+      <c r="P488" s="2" t="inlineStr"/>
+      <c r="Q488" s="2" t="inlineStr">
+        <is>
+          <t>0.07299945064377678</t>
+        </is>
+      </c>
+      <c r="R488" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:54.777576Z</t>
+        </is>
+      </c>
+      <c r="S488" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T488" s="2" t="inlineStr"/>
+      <c r="U488" s="2" t="inlineStr"/>
+      <c r="V488" s="2" t="inlineStr"/>
+      <c r="W488" s="2" t="inlineStr"/>
+      <c r="X488" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y488" s="2" t="inlineStr"/>
+      <c r="Z488" s="2" t="inlineStr"/>
+      <c r="AA488" s="2" t="inlineStr"/>
+      <c r="AB488" s="2" t="inlineStr"/>
+      <c r="AC488" s="2" t="inlineStr"/>
+      <c r="AD488" s="2" t="inlineStr"/>
+      <c r="AE488" s="2" t="inlineStr"/>
+      <c r="AF488" s="2" t="inlineStr"/>
+      <c r="AG488" s="2" t="inlineStr"/>
+      <c r="AH488" s="2" t="inlineStr"/>
+      <c r="AI488" s="2" t="inlineStr"/>
+      <c r="AJ488" s="2" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>d4bc49395c504570</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>718-2026:184442</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J489" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K489" s="2" t="inlineStr"/>
+      <c r="L489" s="2" t="inlineStr">
+        <is>
+          <t>0.509432</t>
+        </is>
+      </c>
+      <c r="M489" s="2" t="inlineStr"/>
+      <c r="N489" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O489" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P489" s="2" t="inlineStr"/>
+      <c r="Q489" s="2" t="inlineStr">
+        <is>
+          <t>-0.05003936563876654</t>
+        </is>
+      </c>
+      <c r="R489" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:44:55.732393Z</t>
+        </is>
+      </c>
+      <c r="S489" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:30Z</t>
+        </is>
+      </c>
+      <c r="T489" s="2" t="inlineStr"/>
+      <c r="U489" s="2" t="inlineStr"/>
+      <c r="V489" s="2" t="inlineStr"/>
+      <c r="W489" s="2" t="inlineStr"/>
+      <c r="X489" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y489" s="2" t="inlineStr"/>
+      <c r="Z489" s="2" t="inlineStr"/>
+      <c r="AA489" s="2" t="inlineStr"/>
+      <c r="AB489" s="2" t="inlineStr"/>
+      <c r="AC489" s="2" t="inlineStr"/>
+      <c r="AD489" s="2" t="inlineStr"/>
+      <c r="AE489" s="2" t="inlineStr"/>
+      <c r="AF489" s="2" t="inlineStr"/>
+      <c r="AG489" s="2" t="inlineStr"/>
+      <c r="AH489" s="2" t="inlineStr"/>
+      <c r="AI489" s="2" t="inlineStr"/>
+      <c r="AJ489" s="2" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>c82d40c416f54402</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181845</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J490" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K490" s="2" t="inlineStr"/>
+      <c r="L490" s="2" t="inlineStr">
+        <is>
+          <t>0.68139</t>
+        </is>
+      </c>
+      <c r="M490" s="2" t="inlineStr"/>
+      <c r="N490" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O490" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P490" s="2" t="inlineStr"/>
+      <c r="Q490" s="2" t="inlineStr">
+        <is>
+          <t>-0.009012476780185685</t>
+        </is>
+      </c>
+      <c r="R490" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:51:31.530644Z</t>
+        </is>
+      </c>
+      <c r="S490" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00Z</t>
+        </is>
+      </c>
+      <c r="T490" s="2" t="inlineStr"/>
+      <c r="U490" s="2" t="inlineStr"/>
+      <c r="V490" s="2" t="inlineStr"/>
+      <c r="W490" s="2" t="inlineStr"/>
+      <c r="X490" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y490" s="2" t="inlineStr"/>
+      <c r="Z490" s="2" t="inlineStr"/>
+      <c r="AA490" s="2" t="inlineStr"/>
+      <c r="AB490" s="2" t="inlineStr"/>
+      <c r="AC490" s="2" t="inlineStr"/>
+      <c r="AD490" s="2" t="inlineStr"/>
+      <c r="AE490" s="2" t="inlineStr"/>
+      <c r="AF490" s="2" t="inlineStr"/>
+      <c r="AG490" s="2" t="inlineStr"/>
+      <c r="AH490" s="2" t="inlineStr"/>
+      <c r="AI490" s="2" t="inlineStr"/>
+      <c r="AJ490" s="2" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>71c8fa6a490940c3</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>3ab056fefe04713e3c294da76c8adb2866b0dc46556ed32322a0426dd344a0e4</t>
+        </is>
+      </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>tennis-surface-elo-v1</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>421-2026:181845</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J491" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K491" s="2" t="inlineStr"/>
+      <c r="L491" s="2" t="inlineStr">
+        <is>
+          <t>0.68139</t>
+        </is>
+      </c>
+      <c r="M491" s="2" t="inlineStr"/>
+      <c r="N491" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O491" s="2" t="inlineStr">
+        <is>
+          <t>0.6904024767801857</t>
+        </is>
+      </c>
+      <c r="P491" s="2" t="inlineStr"/>
+      <c r="Q491" s="2" t="inlineStr">
+        <is>
+          <t>-0.009012476780185685</t>
+        </is>
+      </c>
+      <c r="R491" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:14:35.146859Z</t>
+        </is>
+      </c>
+      <c r="S491" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00Z</t>
+        </is>
+      </c>
+      <c r="T491" s="2" t="inlineStr"/>
+      <c r="U491" s="2" t="inlineStr"/>
+      <c r="V491" s="2" t="inlineStr"/>
+      <c r="W491" s="2" t="inlineStr"/>
+      <c r="X491" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y491" s="2" t="inlineStr"/>
+      <c r="Z491" s="2" t="inlineStr"/>
+      <c r="AA491" s="2" t="inlineStr"/>
+      <c r="AB491" s="2" t="inlineStr"/>
+      <c r="AC491" s="2" t="inlineStr"/>
+      <c r="AD491" s="2" t="inlineStr"/>
+      <c r="AE491" s="2" t="inlineStr"/>
+      <c r="AF491" s="2" t="inlineStr"/>
+      <c r="AG491" s="2" t="inlineStr"/>
+      <c r="AH491" s="2" t="inlineStr"/>
+      <c r="AI491" s="2" t="inlineStr"/>
+      <c r="AJ491" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ461"/>
+  <autoFilter ref="A1:AJ491"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>